--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleLedger.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleLedger.xlsx
@@ -5,6 +5,44 @@
     <sheet name="????" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>{.userName}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.saleStateName}</t>
+  </si>
+  <si>
+    <t>{.useUserName}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59,77 +97,49 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>???</t>
-        </is>
+      <c s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>????</t>
-        </is>
+      <c s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t>SKU</t>
-        </is>
+      <c s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>????</t>
-        </is>
+      <c s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>????</t>
-        </is>
+      <c s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t>???</t>
-        </is>
+      <c s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t>??</t>
-        </is>
+      <c s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{.userName}</t>
-        </is>
+      <c t="s">
+        <v>4</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{.deptName}</t>
-        </is>
+      <c t="s">
+        <v>5</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{.skuNo}</t>
-        </is>
+      <c t="s">
+        <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{.productName}</t>
-        </is>
+      <c t="s">
+        <v>7</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>{.saleStateName}</t>
-        </is>
+      <c t="s">
+        <v>8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{.useUserName}</t>
-        </is>
+      <c t="s">
+        <v>9</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{.qty}</t>
-        </is>
+      <c t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleLedger.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleLedger.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="????" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
-  <si>
-    <t>???</t>
-  </si>
-  <si>
-    <t>????</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>归属人</t>
+  </si>
+  <si>
+    <t>归属部门</t>
   </si>
   <si>
     <t>SKU</t>
   </si>
   <si>
-    <t>??</t>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售状态</t>
+  </si>
+  <si>
+    <t>使用方</t>
+  </si>
+  <si>
+    <t>数量</t>
   </si>
   <si>
     <t>{.userName}</t>
@@ -46,24 +58,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -78,71 +96,405 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c s="1" t="s">
-        <v>1</v>
-      </c>
-      <c s="1" t="s">
-        <v>1</v>
-      </c>
-      <c s="1" t="s">
-        <v>0</v>
-      </c>
-      <c s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2">
-      <c t="s">
-        <v>4</v>
-      </c>
-      <c t="s">
-        <v>5</v>
-      </c>
-      <c t="s">
-        <v>6</v>
-      </c>
-      <c t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c t="s">
+      <c r="D2" t="s">
         <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>